--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,726 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>280</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>杏拼黑F</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>110</v>
+      </c>
+      <c r="G16" t="n">
+        <v>550</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>600</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>120</v>
+      </c>
+      <c r="G18" t="n">
+        <v>600</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-XL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>條紋XL</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>120</v>
+      </c>
+      <c r="G19" t="n">
+        <v>600</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" t="n">
+        <v>400</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>深海藍F</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" t="n">
+        <v>400</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,726 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>280</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>杏拼黑F</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>110</v>
+      </c>
+      <c r="G16" t="n">
+        <v>550</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>600</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>120</v>
+      </c>
+      <c r="G18" t="n">
+        <v>600</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-XL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>條紋XL</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>120</v>
+      </c>
+      <c r="G19" t="n">
+        <v>600</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" t="n">
+        <v>400</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>深海藍F</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" t="n">
+        <v>400</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1079"/>
+  <dimension ref="A1:H1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39278,6 +39278,42 @@
         </is>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>HME03004</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>HME03004-DG-XL</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>居家棉質男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>炭灰色XL</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>46.42575758</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>46.42575758</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1080"/>
+  <dimension ref="A1:H1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39314,6 +39314,402 @@
         </is>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>8640</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>YGJ03001-RFH</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>【罐裝400G】玫瑰四物</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>YGJ03001-OR</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>【罐裝400G】原味</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>990</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1079"/>
+  <dimension ref="A1:H1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39278,6 +39278,402 @@
         </is>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>8640</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>YGJ03001-RFH</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>【罐裝400G】玫瑰四物</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>YGJ03001-OR</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>【罐裝400G】原味</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>990</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1090"/>
+  <dimension ref="A1:H1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39674,6 +39674,906 @@
         </is>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>HFE03002-BR-M</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>摩卡色M</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>39.21801259794172</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>39.21801259794172</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>HFE03006</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>HFE03006-BK-M</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>冰絲面膜速乾三角內褲</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>雅黑色M</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>HFE03006</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>HFE03006-BU-M</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>冰絲面膜速乾三角內褲</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>輕氧藍M</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-380G</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>膚色380G</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>98.70002575295179</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>98.70002575295179</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>HFF03003</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>HFF03003-BK-140G</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>台灣製強力高彈輕量褲襪</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>黑色140G</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>49.95550179211469</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>49.95550179211469</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>HFF02002</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>HFF02002-MT-180G</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>零感無暇雙層校色光腿褲襪</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>中膚色180G</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>144.7181411531399</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>144.7181411531399</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>HMH02001</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>黑色XL</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>167.960547337278</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>335.921094674556</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>31.95664450295537</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>63.91328900591073</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>21.1518585649784</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>21.1518585649784</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>HFE03001-PU-L</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>丁香紫L</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>21.12046868625563</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>42.24093737251127</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>白色L</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>21.2985547648085</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>42.59710952961699</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-L</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>煙粉色L</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>38.91243660609601</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>38.91243660609601</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>【素色】黑灰色XL</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>45.35476676306063</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>45.35476676306063</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>HME03002-SO-GN-XL</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>【素色】淺綠色XL</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>45.36801107170351</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>45.36801107170351</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>HME03002-SO-GY-XL</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>【素色】淺灰色XL</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>45.36252311129687</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>45.36252311129687</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>HME03002-ST-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>【條紋】黑灰色XL</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>45.36088353647321</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>45.36088353647321</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>HME03004</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>HME03004-DG-XL</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>居家棉質男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>炭灰色XL</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>HME03004</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>HME03004-GY-XL</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>居家棉質男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>淺花灰XL</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>藏藍色XL</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>31.95945462463344</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>383.5134554956013</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>21.15949770928919</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>211.5949770928919</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>HFE03001-RD-M</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>中豆紅M</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>21.40793912943965</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>214.0793912943965</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>咖啡色XL</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>31.95871583133227</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>31.95871583133227</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>31.95765307955799</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>95.87295923867397</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-GY-M</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>【立領】灰色M</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>61.01275420499339</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>61.01275420499339</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-WH-M</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>【立領】白色M</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>61.03592250129955</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>122.0718450025991</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12086,6 +12086,402 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>48</v>
+      </c>
+      <c r="F325" t="n">
+        <v>90</v>
+      </c>
+      <c r="G325" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>72</v>
+      </c>
+      <c r="F326" t="n">
+        <v>90</v>
+      </c>
+      <c r="G326" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>YGJ03001-OG</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>【罐裝400G】老薑</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>72</v>
+      </c>
+      <c r="F327" t="n">
+        <v>90</v>
+      </c>
+      <c r="G327" t="n">
+        <v>6480</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>12</v>
+      </c>
+      <c r="F328" t="n">
+        <v>90</v>
+      </c>
+      <c r="G328" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>YGJ03001-SBN</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>【罐裝400G】海燕窩</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>24</v>
+      </c>
+      <c r="F329" t="n">
+        <v>90</v>
+      </c>
+      <c r="G329" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>48</v>
+      </c>
+      <c r="F330" t="n">
+        <v>90</v>
+      </c>
+      <c r="G330" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>YGJ03001-RDL</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>【罐裝400G】紅棗桂圓</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>96</v>
+      </c>
+      <c r="F331" t="n">
+        <v>90</v>
+      </c>
+      <c r="G331" t="n">
+        <v>8640</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>YGJ03001-RFH</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>【罐裝400G】玫瑰四物</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>24</v>
+      </c>
+      <c r="F332" t="n">
+        <v>90</v>
+      </c>
+      <c r="G332" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>12</v>
+      </c>
+      <c r="F333" t="n">
+        <v>90</v>
+      </c>
+      <c r="G333" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>YGJ03001-OS</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>【罐裝400G】桂花</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>24</v>
+      </c>
+      <c r="F334" t="n">
+        <v>90</v>
+      </c>
+      <c r="G334" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>YGJ03001</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>YGJ03001-OR</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>罐裝.ᐟ臺灣天然手工黑糖</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>【罐裝400G】原味</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>11</v>
+      </c>
+      <c r="F335" t="n">
+        <v>90</v>
+      </c>
+      <c r="G335" t="n">
+        <v>990</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1090"/>
+  <dimension ref="A1:H1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39662,6 +39662,906 @@
         </is>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>HFE03002-BR-M</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>摩卡色M</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>39.21801259794172</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>39.21801259794172</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>HFE03006</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>HFE03006-BK-M</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>冰絲面膜速乾三角內褲</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>雅黑色M</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>HFE03006</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>HFE03006-BU-M</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>冰絲面膜速乾三角內褲</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>輕氧藍M</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>34.61910187728937</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-380G</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>膚色380G</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>98.70002575295179</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>98.70002575295179</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>HFF03003</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>HFF03003-BK-140G</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>台灣製強力高彈輕量褲襪</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>黑色140G</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>49.95550179211469</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>49.95550179211469</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>HFF02002</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>HFF02002-MT-180G</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>零感無暇雙層校色光腿褲襪</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>中膚色180G</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>144.7181411531399</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>144.7181411531399</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>HMH02001</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>黑色XL</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>167.960547337278</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>335.921094674556</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>31.95664450295537</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>63.91328900591073</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>21.1518585649784</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>21.1518585649784</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>HFE03001-PU-L</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>丁香紫L</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>21.12046868625563</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>42.24093737251127</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>白色L</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>21.2985547648085</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>42.59710952961699</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-L</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>煙粉色L</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>38.91243660609601</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>38.91243660609601</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>【素色】黑灰色XL</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>45.35476676306063</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>45.35476676306063</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>HME03002-SO-GN-XL</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>【素色】淺綠色XL</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>45.36801107170351</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>45.36801107170351</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>HME03002-SO-GY-XL</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>【素色】淺灰色XL</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>45.36252311129687</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>45.36252311129687</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>HME03002-ST-BK-XL</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>【條紋】黑灰色XL</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>45.36088353647321</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>45.36088353647321</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>HME03004</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>HME03004-DG-XL</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>居家棉質男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>炭灰色XL</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>HME03004</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>HME03004-GY-XL</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>居家棉質男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>淺花灰XL</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>46.4646481629503</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>藏藍色XL</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>31.95945462463344</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>383.5134554956013</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>21.15949770928919</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>211.5949770928919</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>HFE03001-RD-M</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>中豆紅M</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>21.40793912943965</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>214.0793912943965</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>咖啡色XL</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>31.95871583133227</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>31.95871583133227</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>31.95765307955799</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>95.87295923867397</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-GY-M</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>【立領】灰色M</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>61.01275420499339</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>61.01275420499339</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-WH-M</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>【立領】白色M</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>61.03592250129955</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>122.0718450025991</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1440"/>
+  <dimension ref="A1:H1441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52262,6 +52262,42 @@
         </is>
       </c>
     </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E1441" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>169.8738478</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>339.7476956</v>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/入庫.xlsx
+++ b/data/入庫.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1441"/>
+  <dimension ref="A1:H1442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52298,6 +52298,42 @@
         </is>
       </c>
     </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E1442" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>169.8738478</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>339.7476956</v>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
